--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104476_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104476_W2.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.249</v>
+        <v>11.5723</v>
       </c>
       <c r="E2" t="n">
-        <v>8.770200000000001</v>
+        <v>9.24</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4788</v>
+        <v>2.3323</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7601</v>
+        <v>2.7668</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0995</v>
+        <v>1.1027</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6607</v>
+        <v>1.6641</v>
       </c>
       <c r="J2" t="n">
-        <v>2.993</v>
+        <v>2.9645</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1402</v>
+        <v>2.1234</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2329</v>
+        <v>-0.1977</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8078</v>
+        <v>0.8229</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5305</v>
+        <v>-0.1786</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.747</v>
+        <v>-0.2047</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2165</v>
+        <v>0.0261</v>
       </c>
       <c r="V2" t="n">
-        <v>10.3804</v>
+        <v>10.35</v>
       </c>
       <c r="W2" t="n">
-        <v>10.3804</v>
+        <v>10.35</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9091</v>
+        <v>2.0898</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5779</v>
+        <v>3.9688</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6688</v>
+        <v>-1.879</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7559</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1428</v>
+        <v>0.1463</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6131</v>
+        <v>0.6138</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9275</v>
+        <v>1.9041</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9626</v>
+        <v>0.9513</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1716</v>
+        <v>-1.1441</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2758</v>
+        <v>-0.1043</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4688</v>
+        <v>-0.0444</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1929</v>
+        <v>-0.06</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.751</v>
+        <v>1.8373</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0126</v>
+        <v>1.3476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.4897</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1148</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.482</v>
+        <v>-0.477</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5812</v>
+        <v>0.5919</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8012</v>
+        <v>1.7892</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4951</v>
+        <v>0.4859</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.702</v>
+        <v>-1.6744</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3481</v>
+        <v>-0.2775</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5202</v>
+        <v>-0.1652</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1721</v>
+        <v>-0.1122</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9868</v>
+        <v>1.2332</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8777</v>
+        <v>0.1166</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8909</v>
+        <v>1.1166</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3508</v>
+        <v>0.9498</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5801</v>
+        <v>0.8381</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2293</v>
+        <v>0.1117</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6895</v>
+        <v>0.8044</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9194</v>
+        <v>1.1549</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7701</v>
+        <v>-0.3505</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3388</v>
+        <v>0.1454</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3393</v>
+        <v>-0.3168</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9994</v>
+        <v>0.4622</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2032</v>
+        <v>-0.2206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1785</v>
+        <v>-0.2325</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3817</v>
+        <v>0.0119</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.8924</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8512</v>
+        <v>1.0388</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9245</v>
+        <v>3.8156</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7757</v>
+        <v>-2.7768</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1222</v>
+        <v>1.3382</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6824</v>
+        <v>1.5769</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4398</v>
+        <v>-0.2388</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9206</v>
+        <v>3.6427</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0304</v>
+        <v>2.899</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8902</v>
+        <v>0.7436</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7984</v>
+        <v>-2.3045</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.348</v>
+        <v>-1.3221</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4504</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.8562</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8976</v>
+        <v>-2.7316</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5851</v>
+        <v>-0.1416</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0525</v>
+        <v>0.1808</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5326</v>
+        <v>-0.3224</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7226</v>
+        <v>-0.0648</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.173</v>
+        <v>-1.8428</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.7779</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.1231</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8280999999999999</v>
+        <v>2.6852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.112</v>
+        <v>0.4379</v>
       </c>
       <c r="J7" t="n">
-        <v>0.819</v>
+        <v>3.8948</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1602</v>
+        <v>3.0164</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3413</v>
+        <v>0.8783</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1211</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3321</v>
+        <v>-0.3312</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4532</v>
+        <v>-0.4405</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-5.9184</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7126</v>
+        <v>0.6818</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5383</v>
+        <v>0.1808</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1742</v>
+        <v>0.501</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,19 +1033,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7195</v>
+        <v>-0.7171</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7195</v>
+        <v>-0.7171</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1087,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8121</v>
+        <v>-0.8157</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6786</v>
+        <v>0.4231</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4906</v>
+        <v>-1.2389</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7837</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1702</v>
+        <v>1.1744</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3865</v>
+        <v>-0.3827</v>
       </c>
       <c r="J9" t="n">
-        <v>1.649</v>
+        <v>1.636</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8009</v>
+        <v>1.7926</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8653</v>
+        <v>-0.8442</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0433</v>
+        <v>0.0267</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2299</v>
+        <v>-0.0049</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1866</v>
+        <v>0.0316</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="10">
@@ -1189,55 +1189,55 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1322</v>
+        <v>-1.1283</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4532</v>
+        <v>0.4507</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5853</v>
+        <v>-1.5789</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.238</v>
+        <v>-1.235</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0822</v>
+        <v>-1.0799</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5716</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8122</v>
+        <v>-1.8066</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7431</v>
+        <v>-1.5311</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4139</v>
+        <v>-0.2585</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3292</v>
+        <v>-1.2726</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1714</v>
+        <v>-0.1873</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3229</v>
+        <v>-1.3403</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1515</v>
+        <v>1.153</v>
       </c>
       <c r="J11" t="n">
-        <v>0.073</v>
+        <v>0.0413</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1957</v>
+        <v>-1.2248</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2444</v>
+        <v>-0.2285</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5205</v>
+        <v>-0.3031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4869</v>
+        <v>-0.2998</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1896</v>
+        <v>-3.2937</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7842</v>
+        <v>-0.8733</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4054</v>
+        <v>-2.4204</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3976</v>
+        <v>-1.326</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2092</v>
+        <v>-1.1488</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1884</v>
+        <v>-0.1772</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2228</v>
+        <v>-0.7524</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2007</v>
+        <v>-0.7896</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4234</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1749</v>
+        <v>-0.5736</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4099</v>
+        <v>-0.3592</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7649</v>
+        <v>-0.2144</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.153</v>
+        <v>-0.0163</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4386</v>
+        <v>-0.1209</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5916</v>
+        <v>0.1046</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3649</v>
+        <v>-3.351</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.87</v>
+        <v>-1.1517</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4949</v>
+        <v>-2.1993</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3272</v>
+        <v>-2.3963</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1486</v>
+        <v>-0.2096</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1786</v>
+        <v>-2.1867</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.749</v>
+        <v>-1.2375</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7864</v>
+        <v>0.1929</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0373</v>
+        <v>-1.4303</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-1.1588</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3622</v>
+        <v>-0.4025</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2159</v>
+        <v>-0.7563</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.3205</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>0.0858</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0417</v>
+        <v>-0.4063</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5083</v>
+        <v>6.869700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>15.2046</v>
+        <v>15.2361</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.696</v>
+        <v>-8.3665</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5044</v>
+        <v>4.5275</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0113</v>
+        <v>4.0204</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4933000000000004</v>
+        <v>0.5070999999999994</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4751</v>
+        <v>15.2587</v>
       </c>
       <c r="K14" t="n">
-        <v>11.2642</v>
+        <v>11.1363</v>
       </c>
       <c r="L14" t="n">
-        <v>4.2108</v>
+        <v>4.1222</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.9707</v>
+        <v>-10.7311</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.253</v>
+        <v>-7.116000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7174</v>
+        <v>-3.6151</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1341</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3155</v>
+        <v>-0.9749000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1037</v>
+        <v>-0.7459000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2119000000000001</v>
+        <v>-0.229</v>
       </c>
       <c r="V14" t="n">
-        <v>2.185500000000001</v>
+        <v>2.178999999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>16.7116</v>
+        <v>16.6577</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.5261</v>
+        <v>-14.4786</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6857</v>
+        <v>8.3466</v>
       </c>
       <c r="E15" t="n">
-        <v>8.997299999999999</v>
+        <v>9.5519</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3116</v>
+        <v>-1.2052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9121</v>
+        <v>3.9136</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4647</v>
+        <v>-0.4598</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3768</v>
+        <v>4.3734</v>
       </c>
       <c r="J15" t="n">
-        <v>6.064</v>
+        <v>6.0353</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5514</v>
+        <v>1.5373</v>
       </c>
       <c r="L15" t="n">
-        <v>4.5126</v>
+        <v>4.498</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.152</v>
+        <v>-2.1218</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0161</v>
+        <v>-1.9971</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.32</v>
+        <v>0.9778</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1179</v>
+        <v>0.4757</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4379</v>
+        <v>0.5021</v>
       </c>
       <c r="V15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2502</v>
+        <v>3.2963</v>
       </c>
       <c r="E16" t="n">
-        <v>2.199</v>
+        <v>2.4886</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0512</v>
+        <v>0.8078</v>
       </c>
       <c r="G16" t="n">
-        <v>3.688</v>
+        <v>3.6702</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2887</v>
+        <v>2.2809</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3993</v>
+        <v>1.3894</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6864</v>
+        <v>4.6419</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0926</v>
+        <v>3.0714</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5938</v>
+        <v>1.5705</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9984</v>
+        <v>-0.9717</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4889</v>
+        <v>-0.4147</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0434</v>
+        <v>-0.6902</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4455</v>
+        <v>0.2755</v>
       </c>
       <c r="V16" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8309</v>
+        <v>1.4395</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7593</v>
+        <v>5.0802</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9284</v>
+        <v>-3.6407</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2233</v>
+        <v>-0.2292</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0065</v>
+        <v>1.9783</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0465</v>
+        <v>2.0232</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2298</v>
+        <v>-2.2075</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2141</v>
+        <v>0.3924</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0212</v>
+        <v>0.3782</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2353</v>
+        <v>0.0141</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1166</v>
+        <v>0.1861</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4028</v>
+        <v>0.3997</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2862</v>
+        <v>-0.2136</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3747</v>
+        <v>0.3787</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.329</v>
+        <v>-0.3275</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7037</v>
+        <v>0.7062</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6115</v>
+        <v>0.6088</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3242</v>
+        <v>-0.2625</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0161</v>
+        <v>-0.6852</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3844</v>
+        <v>-2.2423</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3682</v>
+        <v>1.5571</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4542</v>
+        <v>0.4565</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0463</v>
+        <v>0.0405</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4079</v>
+        <v>0.416</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2536</v>
+        <v>0.2389</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1416</v>
+        <v>0.1272</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2006</v>
+        <v>0.2176</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1175</v>
+        <v>0.4517</v>
       </c>
       <c r="T19" t="n">
-        <v>0.738</v>
+        <v>-0.0863</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3796</v>
+        <v>0.538</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3838</v>
+        <v>-1.9336</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4048</v>
+        <v>-0.503</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7886</v>
+        <v>-1.4306</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6455</v>
+        <v>-0.3818</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9076</v>
+        <v>-0.1957</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7379</v>
+        <v>-0.1862</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5707</v>
+        <v>-0.2242</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3841</v>
+        <v>0.3792</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1866</v>
+        <v>-0.6035</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2161</v>
+        <v>-0.1576</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2917</v>
+        <v>-0.5749</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9245</v>
+        <v>0.4173</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4619</v>
+        <v>0.3101</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9417</v>
+        <v>-0.2301</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5202</v>
+        <v>0.5402</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>-1.6342</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1266</v>
+        <v>-2.4856</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6081</v>
+        <v>-1.0947</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5185</v>
+        <v>-1.391</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3887</v>
+        <v>-2.1092</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2021</v>
+        <v>-1.7125</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1866</v>
+        <v>-0.3967</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2188</v>
+        <v>-0.2873</v>
       </c>
       <c r="K21" t="n">
-        <v>0.381</v>
+        <v>0.4137</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5998</v>
+        <v>-0.7009</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1699</v>
+        <v>-1.8219</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5831</v>
+        <v>-2.1262</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4132</v>
+        <v>0.3043</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1279</v>
+        <v>-0.0593</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3478</v>
+        <v>-0.214</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4757</v>
+        <v>0.1546</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7317</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6949</v>
+        <v>-2.7589</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8336</v>
+        <v>-0.6792</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8613</v>
+        <v>-2.0797</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1126</v>
+        <v>-2.6425</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.726</v>
+        <v>-0.9103</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3866</v>
+        <v>-1.7322</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2669</v>
+        <v>0.5547</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4156</v>
+        <v>0.3685</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6825</v>
+        <v>0.1862</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8457</v>
+        <v>-3.1971</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1416</v>
+        <v>-1.2788</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2959</v>
+        <v>-1.9184</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2628</v>
+        <v>1.0916</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0212</v>
+        <v>0.8847</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.284</v>
+        <v>0.2069</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9039</v>
+        <v>-3.0582</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1255</v>
+        <v>-1.7111</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7784</v>
+        <v>-1.347</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0396</v>
+        <v>-3.202</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.837</v>
+        <v>-0.9704</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2026</v>
+        <v>-2.2316</v>
       </c>
       <c r="J23" t="n">
-        <v>0.057</v>
+        <v>-1.9722</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3881</v>
+        <v>-0.8693</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4451</v>
+        <v>-1.1029</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0966</v>
+        <v>-1.2298</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4489</v>
+        <v>-0.1011</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.1287</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3625</v>
+        <v>0.1846</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0858</v>
+        <v>-0.0561</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2767</v>
+        <v>0.2407</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8933</v>
+        <v>-3.4059</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3885</v>
+        <v>-1.4943</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5048</v>
+        <v>-1.9116</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1922</v>
+        <v>-2.034</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9638</v>
+        <v>-1.8299</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2284</v>
+        <v>-0.2041</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9428</v>
+        <v>0.046</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8525</v>
+        <v>-0.3932</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0903</v>
+        <v>0.4392</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2494</v>
+        <v>-2.08</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1113</v>
+        <v>-1.4367</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1381</v>
+        <v>-0.6433</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.65</v>
+        <v>0.8558</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7652</v>
+        <v>0.736</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1152</v>
+        <v>0.1198</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3731</v>
+        <v>-3.8832</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8196</v>
+        <v>-2.5187</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5535</v>
+        <v>-1.3644</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3316</v>
+        <v>-2.3477</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4977</v>
+        <v>-0.5078</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8339</v>
+        <v>-1.8399</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8504</v>
+        <v>-0.8891</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0559</v>
+        <v>-0.0764</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7945</v>
+        <v>-0.8126</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4812</v>
+        <v>-1.4587</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1342</v>
+        <v>-0.6249</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.113</v>
+        <v>-0.7599</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0212</v>
+        <v>0.135</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.5083</v>
+        <v>-4.942099999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>7.603499999999999</v>
+        <v>7.277099999999996</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.1119</v>
+        <v>-12.2189</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.5045</v>
+        <v>-4.5274</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.0112</v>
+        <v>-4.0204</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4932999999999998</v>
+        <v>-0.506899999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>10.9708</v>
+        <v>10.7311</v>
       </c>
       <c r="K26" t="n">
-        <v>7.2531</v>
+        <v>7.115900000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>3.7176</v>
+        <v>3.6153</v>
       </c>
       <c r="M26" t="n">
-        <v>-15.4753</v>
+        <v>-15.2586</v>
       </c>
       <c r="N26" t="n">
-        <v>-11.2643</v>
+        <v>-11.1363</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.211</v>
+        <v>-4.122100000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.134100000000001</v>
+        <v>-1.138100000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3156</v>
+        <v>2.9026</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2118999999999995</v>
+        <v>0.2289</v>
       </c>
       <c r="U26" t="n">
-        <v>1.1038</v>
+        <v>2.6735</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W26" t="n">
-        <v>13.4334</v>
+        <v>13.3891</v>
       </c>
       <c r="X26" t="n">
-        <v>-15.6188</v>
+        <v>-15.5681</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104476_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104476_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-14.4786</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104476_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-15.5681</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
